--- a/outputs/v18_cluster_assignments.xlsx
+++ b/outputs/v18_cluster_assignments.xlsx
@@ -11,15 +11,15 @@
     <sheet name="Mismatches" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Assignments!$A$1:$F$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mismatches!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Assignments!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mismatches!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="43">
   <si>
     <t>Recipe</t>
   </si>
@@ -30,6 +30,9 @@
     <t>FS color</t>
   </si>
   <si>
+    <t>ING color</t>
+  </si>
+  <si>
     <t>Corresponding Ingredient cluster</t>
   </si>
   <si>
@@ -63,6 +66,9 @@
     <t>187.800P</t>
   </si>
   <si>
+    <t>teal/green</t>
+  </si>
+  <si>
     <t>ING-C2</t>
   </si>
   <si>
@@ -93,6 +99,9 @@
     <t>185.309P</t>
   </si>
   <si>
+    <t>yellow</t>
+  </si>
+  <si>
     <t>ING-C4</t>
   </si>
   <si>
@@ -108,9 +117,6 @@
     <t>FS-C3</t>
   </si>
   <si>
-    <t>teal/green</t>
-  </si>
-  <si>
     <t>185.294</t>
   </si>
   <si>
@@ -133,9 +139,6 @@
   </si>
   <si>
     <t>FS-C4</t>
-  </si>
-  <si>
-    <t>yellow</t>
   </si>
   <si>
     <t>185.675P</t>
@@ -197,6 +200,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2A9D8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -204,12 +213,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF457B9D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2A9D8F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -252,8 +255,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -550,18 +553,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,466 +583,535 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="C9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
+      <c r="C12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
+      <c r="D20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="F20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="C21" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>27</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>27</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F23"/>
+  <autoFilter ref="A1:G23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="3" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1055,213 +1127,252 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="C5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="C6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="C11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>